--- a/exports/NATIONALUM_full_report.xlsx
+++ b/exports/NATIONALUM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.53</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>106.18</v>
+        <v>100.26</v>
       </c>
       <c r="I2" t="n">
         <v>104.203801311</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.52</v>
+        <v>-8.9</v>
       </c>
       <c r="L2" t="n">
-        <v>5.21</v>
+        <v>10.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>3.08</v>
+        <v>6.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.77</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>11.53</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>104.67</v>
+        <v>109.12</v>
       </c>
       <c r="I3" t="n">
         <v>108.5731720199409</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.4</v>
+        <v>-8.84</v>
       </c>
       <c r="L3" t="n">
-        <v>5.47</v>
+        <v>8.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="N3" t="n">
         <v>5.88</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.37</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44610.38541666666</v>
+        <v>44610.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>114.12</v>
+        <v>112.94</v>
       </c>
       <c r="I4" t="n">
         <v>113.2897138601161</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>4.58</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>3.86</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>118.47</v>
+        <v>123.47</v>
       </c>
       <c r="I5" t="n">
         <v>119.4414365110574</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.9</v>
+        <v>-9.32</v>
       </c>
       <c r="L5" t="n">
-        <v>6.15</v>
+        <v>11.27</v>
       </c>
       <c r="M5" t="n">
         <v>2.45</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>11.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>115.29</v>
+        <v>112.6</v>
       </c>
       <c r="I6" t="n">
         <v>112.7919104204275</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.63</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>7.38</v>
+        <v>9.76</v>
       </c>
       <c r="M6" t="n">
         <v>1.96</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.01</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44643.55208333334</v>
+        <v>44644.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>120.33</v>
+        <v>122.34</v>
       </c>
       <c r="I7" t="n">
         <v>122.2379947231932</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.87</v>
+        <v>-8.65</v>
       </c>
       <c r="L7" t="n">
-        <v>9.56</v>
+        <v>10.83</v>
       </c>
       <c r="M7" t="n">
         <v>1.58</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>121.75</v>
+        <v>116.56</v>
       </c>
       <c r="I8" t="n">
         <v>117.6269018402405</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.48</v>
+        <v>-4.72</v>
       </c>
       <c r="L8" t="n">
         <v>6.8</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.49</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44701.38541666666</v>
+        <v>44701.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>95.45999999999999</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>96.49529697297633</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
         <v>4.16</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>10.11</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>88.61</v>
+        <v>84.55</v>
       </c>
       <c r="I10" t="n">
         <v>87.13312346313171</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.4</v>
+        <v>-12.6</v>
       </c>
       <c r="L10" t="n">
-        <v>10.63</v>
+        <v>13.67</v>
       </c>
       <c r="M10" t="n">
-        <v>2.43</v>
+        <v>2.76</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="O10" t="n">
         <v>4.66</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44749.38541666666</v>
+        <v>44749.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>68.93000000000001</v>
+        <v>72.94</v>
       </c>
       <c r="I11" t="n">
         <v>72.45768443504524</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>18.47</v>
+        <v>13.73</v>
       </c>
       <c r="L11" t="n">
         <v>2.42</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.32</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>75.93000000000001</v>
+        <v>75.39</v>
       </c>
       <c r="I12" t="n">
         <v>75.80324183760624</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>45.83333333333334</v>
+        <v>46</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="L12" t="n">
         <v>7.31</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.9</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44817.55208333334</v>
+        <v>44818.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>79.84999999999999</v>
+        <v>80.34</v>
       </c>
       <c r="I13" t="n">
         <v>80.17270465044621</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.92</v>
+        <v>-6.57</v>
       </c>
       <c r="L13" t="n">
         <v>7.22</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.07</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>77.59</v>
+        <v>75.59</v>
       </c>
       <c r="I14" t="n">
         <v>77.0851894159125</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.42</v>
+        <v>-5.91</v>
       </c>
       <c r="L14" t="n">
-        <v>3.66</v>
+        <v>6.04</v>
       </c>
       <c r="M14" t="n">
         <v>1.6</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>69.61</v>
+        <v>71.62</v>
       </c>
       <c r="I15" t="n">
         <v>71.00620879270774</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>7.91</v>
+        <v>5.25</v>
       </c>
       <c r="L15" t="n">
         <v>2.65</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.95</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>75.88</v>
+        <v>74.22</v>
       </c>
       <c r="I16" t="n">
         <v>74.73069210809945</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
-        <v>5.95</v>
+        <v>3.63</v>
       </c>
       <c r="L16" t="n">
         <v>6.97</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.46</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44922.38541666666</v>
+        <v>44922.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>76.37</v>
+        <v>77.3</v>
       </c>
       <c r="I17" t="n">
         <v>76.42417696688359</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.9</v>
+        <v>-4.15</v>
       </c>
       <c r="L17" t="n">
-        <v>3.42</v>
+        <v>4.74</v>
       </c>
       <c r="M17" t="n">
         <v>1.35</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.16</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>79.59999999999999</v>
+        <v>76.42</v>
       </c>
       <c r="I18" t="n">
         <v>79.16259470140918</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>37</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>2.98</v>
+        <v>-1.14</v>
       </c>
       <c r="L18" t="n">
         <v>1.97</v>
@@ -1467,7 +1682,7 @@
         <v>1.32</v>
       </c>
       <c r="N18" t="n">
-        <v>2.89</v>
+        <v>3.38</v>
       </c>
       <c r="O18" t="n">
         <v>6.69</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.9</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44977.55208333334</v>
+        <v>44978.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>79.65000000000001</v>
+        <v>80.34</v>
       </c>
       <c r="I19" t="n">
         <v>79.73259383923977</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.23</v>
+        <v>-5.13</v>
       </c>
       <c r="L19" t="n">
-        <v>4.87</v>
+        <v>6.08</v>
       </c>
       <c r="M19" t="n">
         <v>0.63</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>5.12</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>76.66</v>
+        <v>74.95</v>
       </c>
       <c r="I20" t="n">
         <v>76.61101993455976</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.58</v>
+        <v>-6.71</v>
       </c>
       <c r="L20" t="n">
-        <v>4.82</v>
+        <v>7.13</v>
       </c>
       <c r="M20" t="n">
         <v>0.37</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.19</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>76.70999999999999</v>
+        <v>80.34</v>
       </c>
       <c r="I21" t="n">
         <v>80.20723182093535</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.35</v>
+        <v>-7.19</v>
       </c>
       <c r="L21" t="n">
-        <v>3.14</v>
+        <v>7.24</v>
       </c>
       <c r="M21" t="n">
         <v>0.33</v>
       </c>
       <c r="N21" t="n">
-        <v>0.45</v>
+        <v>5.31</v>
       </c>
       <c r="O21" t="n">
         <v>-0.38</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45002.55208333334</v>
+        <v>45005.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>81.02</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>78.11437317285169</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>0.85</v>
+        <v>-3.66</v>
       </c>
       <c r="L22" t="n">
         <v>4.75</v>
@@ -1695,7 +1958,7 @@
         <v>1.55</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.69</v>
       </c>
       <c r="O22" t="n">
         <v>5.31</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.45</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45027.38541666666</v>
+        <v>45027.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>78.48</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>78.9461411473503</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4</v>
+        <v>-2.34</v>
       </c>
       <c r="L23" t="n">
         <v>6.07</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.3</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45050.55208333334</v>
+        <v>45051.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>81.02</v>
+        <v>78.72</v>
       </c>
       <c r="I24" t="n">
         <v>78.80662117854811</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>2.29</v>
+        <v>-0.62</v>
       </c>
       <c r="L24" t="n">
         <v>2.05</v>
@@ -1809,7 +2096,7 @@
         <v>0.42</v>
       </c>
       <c r="N24" t="n">
-        <v>1.54</v>
+        <v>3.32</v>
       </c>
       <c r="O24" t="n">
         <v>0.88</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.41</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45071.55208333334</v>
+        <v>45072.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>78.92</v>
+        <v>82.69</v>
       </c>
       <c r="I25" t="n">
         <v>81.35724552061235</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.25</v>
+        <v>-5.04</v>
       </c>
       <c r="L25" t="n">
-        <v>3.48</v>
+        <v>6.9</v>
       </c>
       <c r="M25" t="n">
         <v>0.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.62</v>
+        <v>4.95</v>
       </c>
       <c r="O25" t="n">
         <v>-3.32</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.43</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>81.95</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>80.76936364865564</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.89</v>
+        <v>-2.43</v>
       </c>
       <c r="L26" t="n">
         <v>4.56</v>
@@ -1923,7 +2234,7 @@
         <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>2.36</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
         <v>4.95</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.73</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45119.55208333334</v>
+        <v>45120.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>82.93000000000001</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>83.03663675213247</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.79</v>
+        <v>-3.27</v>
       </c>
       <c r="L27" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="M27" t="n">
         <v>0.97</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.24</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45140.38541666666</v>
+        <v>45140.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>90.67</v>
+        <v>90.22</v>
       </c>
       <c r="I28" t="n">
         <v>90.38284277638441</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>8.82</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>1.18</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>4.96</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45147.38541666666</v>
+        <v>45147.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>93.11</v>
+        <v>94.88</v>
       </c>
       <c r="I29" t="n">
         <v>94.69667761897279</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.2</v>
+        <v>-5.17</v>
       </c>
       <c r="L29" t="n">
-        <v>4.29</v>
+        <v>5.26</v>
       </c>
       <c r="M29" t="n">
         <v>0.57</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.34</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>92.18000000000001</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>89.81186394906649</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.85</v>
+        <v>-6.36</v>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>7.02</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2</v>
+        <v>2.02</v>
       </c>
       <c r="N30" t="n">
-        <v>1.76</v>
+        <v>3.71</v>
       </c>
       <c r="O30" t="n">
         <v>2.16</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.76</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>88.70999999999999</v>
+        <v>89.78</v>
       </c>
       <c r="I31" t="n">
         <v>89.21363409645423</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>0.16</v>
+        <v>-1.05</v>
       </c>
       <c r="L31" t="n">
         <v>1.65</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.19</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>99.43000000000001</v>
+        <v>94.88</v>
       </c>
       <c r="I32" t="n">
         <v>95.66763513094874</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>10.75</v>
+        <v>5.68</v>
       </c>
       <c r="L32" t="n">
         <v>1.36</v>
@@ -2265,7 +2648,7 @@
         <v>0.39</v>
       </c>
       <c r="N32" t="n">
-        <v>1.95</v>
+        <v>6.26</v>
       </c>
       <c r="O32" t="n">
         <v>2.65</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.38</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>93.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>95.74239380220814</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K33" t="n">
-        <v>1.19</v>
+        <v>-2.16</v>
       </c>
       <c r="L33" t="n">
         <v>5.98</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.17</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>95.56</v>
+        <v>92.77</v>
       </c>
       <c r="I34" t="n">
         <v>93.17049670488109</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.41</v>
+        <v>-4.29</v>
       </c>
       <c r="L34" t="n">
-        <v>3.23</v>
+        <v>4.45</v>
       </c>
       <c r="M34" t="n">
         <v>0.85</v>
       </c>
       <c r="N34" t="n">
-        <v>1.01</v>
+        <v>3.13</v>
       </c>
       <c r="O34" t="n">
         <v>4.07</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.19</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>91.79000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>93.00022599884343</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K35" t="n">
-        <v>1.06</v>
+        <v>-1.64</v>
       </c>
       <c r="L35" t="n">
         <v>3.64</v>
@@ -2436,7 +2855,7 @@
         <v>1.52</v>
       </c>
       <c r="N35" t="n">
-        <v>2.31</v>
+        <v>3.31</v>
       </c>
       <c r="O35" t="n">
         <v>-3.13</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.04</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>108.83</v>
+        <v>101.73</v>
       </c>
       <c r="I36" t="n">
         <v>103.4182855051145</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>15.42</v>
+        <v>7.89</v>
       </c>
       <c r="L36" t="n">
         <v>1.82</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>14.55</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>115.05</v>
+        <v>123.42</v>
       </c>
       <c r="I37" t="n">
         <v>115.762771442085</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-13.09</v>
+        <v>-21.32</v>
       </c>
       <c r="L37" t="n">
-        <v>14.34</v>
+        <v>22.04</v>
       </c>
       <c r="M37" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="N37" t="n">
-        <v>7.26</v>
+        <v>10.29</v>
       </c>
       <c r="O37" t="n">
         <v>-8.050000000000001</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.57</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>130.27</v>
+        <v>122.29</v>
       </c>
       <c r="I38" t="n">
         <v>125.2391492396878</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>5.55</v>
+        <v>-0.92</v>
       </c>
       <c r="L38" t="n">
         <v>5.56</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>15.19</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>139.23</v>
+        <v>141.58</v>
       </c>
       <c r="I39" t="n">
         <v>140.861701344214</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-13.85</v>
+        <v>-15.77</v>
       </c>
       <c r="L39" t="n">
-        <v>14.01</v>
+        <v>18.82</v>
       </c>
       <c r="M39" t="n">
         <v>2.49</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.84</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>143.78</v>
+        <v>140.01</v>
       </c>
       <c r="I40" t="n">
         <v>143.1435653544935</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>1.55</v>
+        <v>-1.11</v>
       </c>
       <c r="L40" t="n">
         <v>2.15</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>16.38</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>153.67</v>
+        <v>163.51</v>
       </c>
       <c r="I41" t="n">
         <v>158.3975297194426</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.76</v>
+        <v>-16.78</v>
       </c>
       <c r="L41" t="n">
-        <v>12.13</v>
+        <v>18.39</v>
       </c>
       <c r="M41" t="n">
         <v>3.03</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>15.27</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>154.06</v>
+        <v>150.15</v>
       </c>
       <c r="I42" t="n">
         <v>150.357663390455</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.78</v>
+        <v>-8.17</v>
       </c>
       <c r="L42" t="n">
         <v>9.369999999999999</v>
@@ -2835,7 +3338,7 @@
         <v>0.16</v>
       </c>
       <c r="N42" t="n">
-        <v>3.47</v>
+        <v>3.91</v>
       </c>
       <c r="O42" t="n">
         <v>3.83</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>10.84</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>149.95</v>
+        <v>155.29</v>
       </c>
       <c r="I43" t="n">
         <v>151.1100057431687</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>0.13</v>
+        <v>-3.42</v>
       </c>
       <c r="L43" t="n">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="M43" t="n">
         <v>1.81</v>
       </c>
       <c r="N43" t="n">
-        <v>5.66</v>
+        <v>5.91</v>
       </c>
       <c r="O43" t="n">
         <v>-3.91</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.4</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>178.54</v>
+        <v>170.95</v>
       </c>
       <c r="I44" t="n">
         <v>173.7835018846575</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K44" t="n">
-        <v>14.97</v>
+        <v>10.08</v>
       </c>
       <c r="L44" t="n">
         <v>3.16</v>
@@ -2949,7 +3476,7 @@
         <v>0.91</v>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>3.13</v>
       </c>
       <c r="O44" t="n">
         <v>5.91</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>10.88</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45426.38541666666</v>
+        <v>45426.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>181.62</v>
+        <v>185</v>
       </c>
       <c r="I45" t="n">
         <v>182.3697708831588</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.24</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>6.76</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>0.77</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.99</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>192.35</v>
+        <v>161.55</v>
       </c>
       <c r="I46" t="n">
         <v>181.329513369125</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>3.97</v>
+        <v>-12.68</v>
       </c>
       <c r="L46" t="n">
-        <v>1.83</v>
+        <v>22.12</v>
       </c>
       <c r="M46" t="n">
         <v>1.49</v>
       </c>
       <c r="N46" t="n">
-        <v>3.59</v>
+        <v>17.87</v>
       </c>
       <c r="O46" t="n">
         <v>6.54</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>21.93</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>190.93</v>
+        <v>194.29</v>
       </c>
       <c r="I47" t="n">
         <v>191.7109251161133</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>-18.19</v>
+        <v>-20.27</v>
       </c>
       <c r="L47" t="n">
-        <v>20</v>
+        <v>20.94</v>
       </c>
       <c r="M47" t="n">
         <v>1.89</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.71</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45491.38541666666</v>
+        <v>45491.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>188.77</v>
+        <v>187.69</v>
       </c>
       <c r="I48" t="n">
         <v>188.6304682499228</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.84</v>
+        <v>-3.4</v>
       </c>
       <c r="L48" t="n">
         <v>3.49</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.92</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45530.38541666666</v>
+        <v>45530.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>175.04</v>
+        <v>177.91</v>
       </c>
       <c r="I49" t="n">
         <v>175.7884739239774</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>6.74</v>
+        <v>5.21</v>
       </c>
       <c r="L49" t="n">
         <v>4.54</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.22</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>170.36</v>
+        <v>165.87</v>
       </c>
       <c r="I50" t="n">
         <v>170.2443932076017</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.24</v>
+        <v>-6.77</v>
       </c>
       <c r="L50" t="n">
-        <v>5</v>
+        <v>7.53</v>
       </c>
       <c r="M50" t="n">
         <v>2.07</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.57</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>175.56</v>
+        <v>178.84</v>
       </c>
       <c r="I51" t="n">
         <v>176.7674904115743</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.84</v>
+        <v>-7.82</v>
       </c>
       <c r="L51" t="n">
-        <v>6.16</v>
+        <v>9.44</v>
       </c>
       <c r="M51" t="n">
         <v>0.97</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.98</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>220.78</v>
+        <v>216.02</v>
       </c>
       <c r="I52" t="n">
         <v>219.7772452660388</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K52" t="n">
-        <v>23.45</v>
+        <v>20.79</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>10.29</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45610.55208333334</v>
+        <v>45614.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>214.91</v>
+        <v>240.27</v>
       </c>
       <c r="I53" t="n">
         <v>234.5552346446645</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>0.51</v>
+        <v>-11.23</v>
       </c>
       <c r="L53" t="n">
-        <v>4.55</v>
+        <v>12.36</v>
       </c>
       <c r="M53" t="n">
         <v>4.92</v>
       </c>
       <c r="N53" t="n">
-        <v>0.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O53" t="n">
         <v>-2.79</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>14.53</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45637.55208333334</v>
+        <v>45638.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>243.8</v>
+        <v>226.93</v>
       </c>
       <c r="I54" t="n">
         <v>230.2702575258832</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>1.47</v>
+        <v>-5.55</v>
       </c>
       <c r="L54" t="n">
         <v>8.31</v>
@@ -3519,7 +4166,7 @@
         <v>1.64</v>
       </c>
       <c r="N54" t="n">
-        <v>2.93</v>
+        <v>7.19</v>
       </c>
       <c r="O54" t="n">
         <v>8.800000000000001</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>13.03</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>200.42</v>
+        <v>205.8</v>
       </c>
       <c r="I55" t="n">
         <v>203.9953001486909</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K55" t="n">
-        <v>11.68</v>
+        <v>9.31</v>
       </c>
       <c r="L55" t="n">
         <v>8.619999999999999</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.31</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45684.55208333334</v>
+        <v>45685.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>192.49</v>
+        <v>190.32</v>
       </c>
       <c r="I56" t="n">
         <v>192.2963148812246</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.47</v>
+        <v>-7.52</v>
       </c>
       <c r="L56" t="n">
-        <v>6.75</v>
+        <v>10.93</v>
       </c>
       <c r="M56" t="n">
         <v>1.18</v>
       </c>
       <c r="N56" t="n">
-        <v>3.11</v>
+        <v>3.68</v>
       </c>
       <c r="O56" t="n">
         <v>2.64</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.26</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45708.55208333334</v>
+        <v>45709.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>192.6</v>
+        <v>201.83</v>
       </c>
       <c r="I57" t="n">
         <v>195.9249572738906</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.2</v>
+        <v>-6.05</v>
       </c>
       <c r="L57" t="n">
-        <v>4.89</v>
+        <v>6.07</v>
       </c>
       <c r="M57" t="n">
         <v>2.49</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>11.24</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45712.55208333334</v>
+        <v>45713.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>189.1</v>
+        <v>183.1</v>
       </c>
       <c r="I58" t="n">
         <v>183.5114881664063</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.31</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>6.44</v>
+        <v>9.68</v>
       </c>
       <c r="M58" t="n">
         <v>1.18</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>11.68</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>192.09</v>
+        <v>193.68</v>
       </c>
       <c r="I59" t="n">
         <v>193.4173639616212</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.91</v>
+        <v>-5.78</v>
       </c>
       <c r="L59" t="n">
-        <v>6.13</v>
+        <v>6.91</v>
       </c>
       <c r="M59" t="n">
         <v>1.19</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.53</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45741.38541666666</v>
+        <v>45741.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>181.39</v>
+        <v>180.42</v>
       </c>
       <c r="I60" t="n">
         <v>181.1165253645032</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.35</v>
+        <v>-6.85</v>
       </c>
       <c r="L60" t="n">
         <v>7.01</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.63</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45768.38541666666</v>
+        <v>45768.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>159.55</v>
+        <v>161.36</v>
       </c>
       <c r="I61" t="n">
         <v>160.0165137495109</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K61" t="n">
-        <v>11.57</v>
+        <v>10.56</v>
       </c>
       <c r="L61" t="n">
         <v>1.41</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.81</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>186.1</v>
+        <v>181.94</v>
       </c>
       <c r="I62" t="n">
         <v>182.3755620310537</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>58</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>15.33</v>
+        <v>12.75</v>
       </c>
       <c r="L62" t="n">
         <v>7.66</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>6.27</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45834.38541666666</v>
+        <v>45834.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>189.75</v>
+        <v>193.3</v>
       </c>
       <c r="I63" t="n">
         <v>191.5783176371866</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.29</v>
+        <v>-6.24</v>
       </c>
       <c r="L63" t="n">
-        <v>5.69</v>
+        <v>6.9</v>
       </c>
       <c r="M63" t="n">
         <v>0.87</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.7</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>193.5</v>
+        <v>187.6</v>
       </c>
       <c r="I64" t="n">
         <v>191.2025392751144</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1</v>
+        <v>-2.95</v>
       </c>
       <c r="L64" t="n">
         <v>4.17</v>
@@ -4089,7 +4856,7 @@
         <v>0.34</v>
       </c>
       <c r="N64" t="n">
-        <v>2.52</v>
+        <v>3.21</v>
       </c>
       <c r="O64" t="n">
         <v>3.08</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.46</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>188.25</v>
+        <v>191.36</v>
       </c>
       <c r="I65" t="n">
         <v>190.2396179896485</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.35</v>
+        <v>-2</v>
       </c>
       <c r="L65" t="n">
         <v>3.22</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.4</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>209.8</v>
+        <v>205.87</v>
       </c>
       <c r="I66" t="n">
         <v>207.2120404258602</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K66" t="n">
-        <v>9.640000000000001</v>
+        <v>7.58</v>
       </c>
       <c r="L66" t="n">
         <v>3.92</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>5.95</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45929.55208333334</v>
+        <v>45930.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>204.2</v>
+        <v>212.45</v>
       </c>
       <c r="I67" t="n">
         <v>211.2748372088012</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.2</v>
       </c>
       <c r="L67" t="n">
-        <v>2.19</v>
+        <v>4.63</v>
       </c>
       <c r="M67" t="n">
         <v>0.28</v>
       </c>
       <c r="N67" t="n">
-        <v>1.88</v>
+        <v>5.02</v>
       </c>
       <c r="O67" t="n">
         <v>-1.61</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.56</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>258.74</v>
+        <v>252.61</v>
       </c>
       <c r="I68" t="n">
         <v>253.941846852125</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K68" t="n">
-        <v>21.79</v>
+        <v>18.9</v>
       </c>
       <c r="L68" t="n">
         <v>3.88</v>
@@ -4317,7 +5132,7 @@
         <v>1.94</v>
       </c>
       <c r="N68" t="n">
-        <v>2.22</v>
+        <v>3.19</v>
       </c>
       <c r="O68" t="n">
         <v>5.02</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>6.37</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45989.55208333334</v>
+        <v>45992.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>260.4</v>
+        <v>265.5</v>
       </c>
       <c r="I69" t="n">
         <v>263.3368144651104</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.08</v>
+        <v>-5.1</v>
       </c>
       <c r="L69" t="n">
-        <v>5.11</v>
+        <v>5.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0.6</v>
+        <v>1.42</v>
       </c>
       <c r="N69" t="n">
         <v>1.47</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>5.05</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>428.3</v>
+        <v>387.55</v>
       </c>
       <c r="I70" t="n">
         <v>396.739882246237</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K70" t="n">
-        <v>61.32</v>
+        <v>45.97</v>
       </c>
       <c r="L70" t="n">
         <v>2.34</v>
       </c>
       <c r="M70" t="n">
-        <v>1.99</v>
+        <v>3.36</v>
       </c>
       <c r="N70" t="n">
-        <v>5.64</v>
+        <v>10.58</v>
       </c>
       <c r="O70" t="n">
         <v>1.46</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>13.73</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46078.38541666666</v>
+        <v>46078.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>358.45</v>
+        <v>360.9</v>
       </c>
       <c r="I71" t="n">
         <v>359.5385423106853</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>7.51</v>
+        <v>6.88</v>
       </c>
       <c r="L71" t="n">
         <v>6.8</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.02</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46097.38541666666</v>
+        <v>46097.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>372.7</v>
+        <v>371.7</v>
       </c>
       <c r="I72" t="n">
         <v>372.1894213496669</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>3.27</v>
+        <v>2.99</v>
       </c>
       <c r="L72" t="n">
         <v>5.51</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>10.69</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46108.55208333334</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>371</v>
+        <v>389.8</v>
       </c>
       <c r="I73" t="n">
         <v>387.8839083099052</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>0.19</v>
+        <v>-4.87</v>
       </c>
       <c r="L73" t="n">
         <v>6.75</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>10.09</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>432.95</v>
+        <v>414.3</v>
       </c>
       <c r="I74" t="n">
         <v>418.6964995880217</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K74" t="n">
-        <v>11.07</v>
+        <v>6.29</v>
       </c>
       <c r="L74" t="n">
         <v>3.53</v>
@@ -4659,7 +5546,7 @@
         <v>1.42</v>
       </c>
       <c r="N74" t="n">
-        <v>2.89</v>
+        <v>8.68</v>
       </c>
       <c r="O74" t="n">
         <v>3.83</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>8.69</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>417.75</v>
+        <v>433.7</v>
       </c>
       <c r="I75" t="n">
         <v>419.8971771584015</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.83</v>
+        <v>-4.68</v>
       </c>
       <c r="L75" t="n">
-        <v>4.38</v>
+        <v>5.66</v>
       </c>
       <c r="M75" t="n">
         <v>1.33</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>6.97</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>413.5</v>
+        <v>393.3</v>
       </c>
       <c r="I76" t="n">
         <v>411.2212584227586</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.66</v>
+        <v>-9.32</v>
       </c>
       <c r="L76" t="n">
-        <v>4.88</v>
+        <v>9.41</v>
       </c>
       <c r="M76" t="n">
         <v>0.46</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>10.73</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46216.55208333334</v>
+        <v>46217.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>354.95</v>
+        <v>363.25</v>
       </c>
       <c r="I77" t="n">
         <v>356.4402377251117</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K77" t="n">
-        <v>9.75</v>
+        <v>7.64</v>
       </c>
       <c r="L77" t="n">
         <v>4.88</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>6.76</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46219.55208333334</v>
+        <v>46220.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>355</v>
+        <v>340.85</v>
       </c>
       <c r="I78" t="n">
         <v>343.107209546899</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.27</v>
+        <v>-6.17</v>
       </c>
       <c r="L78" t="n">
-        <v>2.66</v>
+        <v>6.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N78" t="n">
-        <v>1.78</v>
+        <v>3.85</v>
       </c>
       <c r="O78" t="n">
         <v>2.69</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>8.34</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>350.5</v>
+        <v>361.35</v>
       </c>
       <c r="I79" t="n">
         <v>353.2408095671683</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.83</v>
+        <v>-6.01</v>
       </c>
       <c r="L79" t="n">
-        <v>4.37</v>
+        <v>6.35</v>
       </c>
       <c r="M79" t="n">
-        <v>0.89</v>
+        <v>2.13</v>
       </c>
       <c r="N79" t="n">
-        <v>3.01</v>
+        <v>4.15</v>
       </c>
       <c r="O79" t="n">
         <v>-3.85</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>6.28</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46247.55208333334</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>400.95</v>
+        <v>378.45</v>
       </c>
       <c r="I80" t="n">
         <v>391.3194972735246</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K80" t="n">
-        <v>10.96</v>
+        <v>4.73</v>
       </c>
       <c r="L80" t="n">
         <v>2.17</v>
       </c>
       <c r="M80" t="n">
-        <v>2.01</v>
+        <v>5.57</v>
       </c>
       <c r="N80" t="n">
-        <v>4.29</v>
+        <v>6.24</v>
       </c>
       <c r="O80" t="n">
         <v>4.15</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>100</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7163,7 +8142,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.1</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="6">
@@ -7173,7 +8152,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -7183,7 +8162,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -7193,7 +8172,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7203,7 +8182,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -7213,7 +8192,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -7223,7 +8202,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -7233,7 +8212,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -7243,7 +8222,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.7</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="14">
@@ -7253,7 +8232,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.79</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="15">
@@ -7263,7 +8242,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.23</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="16">
@@ -7273,7 +8252,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.72</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="17">
@@ -7283,7 +8262,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61.32</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="18">
@@ -7293,7 +8272,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="19">
@@ -7303,7 +8282,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.21</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="20">
@@ -7313,7 +8292,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.56</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="21">
@@ -7323,7 +8302,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="22">
@@ -7333,7 +8312,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -7343,7 +8322,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -7353,7 +8332,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="25">
@@ -7363,7 +8342,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.95</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="26">
@@ -7373,7 +8352,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.06</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="27">
@@ -7383,7 +8362,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.67</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="28">
@@ -7393,7 +8372,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
